--- a/New_Code/matrices.xlsx
+++ b/New_Code/matrices.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipmc\Desktop\Code_hERG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF471CC-3B10-4638-9F3B-D2B7A8F3F82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12345" activeTab="2"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrice des tailles" sheetId="1" r:id="rId1"/>
@@ -151,7 +152,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
@@ -218,7 +219,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -233,7 +234,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -516,7 +517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1888,7 +1889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3260,23 +3261,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -4434,7 +4435,7 @@
     </row>
     <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>

--- a/New_Code/matrices.xlsx
+++ b/New_Code/matrices.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipmc\Desktop\Code_hERG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF471CC-3B10-4638-9F3B-D2B7A8F3F82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12345" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Matrice des tailles" sheetId="1" r:id="rId1"/>
@@ -152,7 +151,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
@@ -219,7 +218,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -234,7 +233,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -517,7 +516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1889,7 +1888,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3261,23 +3260,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -4219,23 +4218,23 @@
       <c r="O15" s="4">
         <v>0</v>
       </c>
-      <c r="P15" s="6">
-        <v>1</v>
+      <c r="P15" s="7">
+        <v>2</v>
       </c>
       <c r="Q15" s="6">
         <v>1</v>
       </c>
-      <c r="R15" s="6">
-        <v>1</v>
+      <c r="R15" s="7">
+        <v>2</v>
       </c>
       <c r="S15" s="6">
         <v>1</v>
       </c>
-      <c r="T15" s="6">
-        <v>1</v>
-      </c>
-      <c r="U15" s="6">
-        <v>1</v>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
@@ -4281,8 +4280,8 @@
       <c r="N16" s="6">
         <v>1</v>
       </c>
-      <c r="O16" s="6">
-        <v>1</v>
+      <c r="O16" s="7">
+        <v>2</v>
       </c>
       <c r="P16" s="4">
         <v>0</v>
@@ -4411,8 +4410,8 @@
       <c r="N18" s="6">
         <v>1</v>
       </c>
-      <c r="O18" s="6">
-        <v>1</v>
+      <c r="O18" s="7">
+        <v>2</v>
       </c>
       <c r="P18" s="5">
         <v>0</v>
@@ -4435,7 +4434,7 @@
     </row>
     <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5">
         <v>0</v>
@@ -4541,8 +4540,8 @@
       <c r="N20" s="6">
         <v>1</v>
       </c>
-      <c r="O20" s="6">
-        <v>1</v>
+      <c r="O20" s="5">
+        <v>0</v>
       </c>
       <c r="P20" s="7">
         <v>2</v>
@@ -4606,8 +4605,8 @@
       <c r="N21" s="6">
         <v>1</v>
       </c>
-      <c r="O21" s="6">
-        <v>1</v>
+      <c r="O21" s="5">
+        <v>0</v>
       </c>
       <c r="P21" s="7">
         <v>2</v>

--- a/New_Code/matrices.xlsx
+++ b/New_Code/matrices.xlsx
@@ -1,25 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipmc\Desktop\Code_hERG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guillaume\Desktop\hERG\New_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BFDBFC-FBBC-46A7-85EF-248BBF1222D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12345" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrice des tailles" sheetId="1" r:id="rId1"/>
     <sheet name="Matrice d'hydrophobicité" sheetId="2" r:id="rId2"/>
     <sheet name="Matrice des charges" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -151,7 +163,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0_ ;\-0\ "/>
   </numFmts>
@@ -209,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -218,7 +230,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -233,10 +245,7 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,8 +525,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -589,61 +598,61 @@
       <c r="B2" s="11">
         <v>0</v>
       </c>
-      <c r="C2" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
-      <c r="G2" s="14">
-        <v>1</v>
-      </c>
-      <c r="H2" s="14">
-        <v>1</v>
-      </c>
-      <c r="I2" s="13">
-        <v>0</v>
-      </c>
-      <c r="J2" s="14">
-        <v>1</v>
-      </c>
-      <c r="K2" s="14">
-        <v>1</v>
-      </c>
-      <c r="L2" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="M2" s="14">
-        <v>1</v>
-      </c>
-      <c r="N2" s="14">
-        <v>1</v>
-      </c>
-      <c r="O2" s="14">
-        <v>1</v>
-      </c>
-      <c r="P2" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>0</v>
-      </c>
-      <c r="R2" s="13">
-        <v>0</v>
-      </c>
-      <c r="S2" s="12">
-        <v>2</v>
-      </c>
-      <c r="T2" s="14">
-        <v>1</v>
-      </c>
-      <c r="U2" s="13">
+      <c r="C2" s="11">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1</v>
+      </c>
+      <c r="H2" s="11">
+        <v>1</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1</v>
+      </c>
+      <c r="K2" s="11">
+        <v>1</v>
+      </c>
+      <c r="L2" s="11">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11">
+        <v>1</v>
+      </c>
+      <c r="N2" s="11">
+        <v>1</v>
+      </c>
+      <c r="O2" s="11">
+        <v>1</v>
+      </c>
+      <c r="P2" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>0</v>
+      </c>
+      <c r="R2" s="11">
+        <v>0</v>
+      </c>
+      <c r="S2" s="11">
+        <v>2</v>
+      </c>
+      <c r="T2" s="11">
+        <v>1</v>
+      </c>
+      <c r="U2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -651,64 +660,64 @@
       <c r="A3" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="12">
-        <v>1.5</v>
+      <c r="B3" s="11">
+        <v>2</v>
       </c>
       <c r="C3" s="11">
         <v>0</v>
       </c>
-      <c r="D3" s="14">
-        <v>1</v>
-      </c>
-      <c r="E3" s="14">
-        <v>1</v>
-      </c>
-      <c r="F3" s="14">
-        <v>1</v>
-      </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="12">
-        <v>2</v>
-      </c>
-      <c r="J3" s="13">
-        <v>0</v>
-      </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
-        <v>0</v>
-      </c>
-      <c r="M3" s="13">
-        <v>0</v>
-      </c>
-      <c r="N3" s="13">
-        <v>0</v>
-      </c>
-      <c r="O3" s="13">
-        <v>0</v>
-      </c>
-      <c r="P3" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="14">
-        <v>1</v>
-      </c>
-      <c r="R3" s="14">
-        <v>1</v>
-      </c>
-      <c r="S3" s="13">
-        <v>0</v>
-      </c>
-      <c r="T3" s="13">
-        <v>0</v>
-      </c>
-      <c r="U3" s="14">
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11">
+        <v>1</v>
+      </c>
+      <c r="I3" s="11">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0</v>
+      </c>
+      <c r="K3" s="11">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11">
+        <v>0</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0</v>
+      </c>
+      <c r="O3" s="11">
+        <v>0</v>
+      </c>
+      <c r="P3" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="11">
+        <v>1</v>
+      </c>
+      <c r="R3" s="11">
+        <v>1</v>
+      </c>
+      <c r="S3" s="11">
+        <v>0</v>
+      </c>
+      <c r="T3" s="11">
+        <v>0</v>
+      </c>
+      <c r="U3" s="11">
         <v>1</v>
       </c>
     </row>
@@ -716,64 +725,64 @@
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13">
-        <v>0</v>
-      </c>
-      <c r="C4" s="14">
+      <c r="B4" s="11">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11">
         <v>1</v>
       </c>
       <c r="D4" s="11">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
-        <v>0</v>
-      </c>
-      <c r="I4" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="13">
-        <v>0</v>
-      </c>
-      <c r="K4" s="13">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13">
-        <v>0</v>
-      </c>
-      <c r="M4" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="N4" s="13">
-        <v>0</v>
-      </c>
-      <c r="O4" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="P4" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-      <c r="R4" s="13">
-        <v>0</v>
-      </c>
-      <c r="S4" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="T4" s="14">
-        <v>1</v>
-      </c>
-      <c r="U4" s="13">
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11">
+        <v>0</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0</v>
+      </c>
+      <c r="O4" s="11">
+        <v>1</v>
+      </c>
+      <c r="P4" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>0</v>
+      </c>
+      <c r="R4" s="11">
+        <v>0</v>
+      </c>
+      <c r="S4" s="11">
+        <v>2</v>
+      </c>
+      <c r="T4" s="11">
+        <v>1</v>
+      </c>
+      <c r="U4" s="11">
         <v>0</v>
       </c>
     </row>
@@ -781,64 +790,64 @@
       <c r="A5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="13">
-        <v>0</v>
-      </c>
-      <c r="C5" s="14">
-        <v>1</v>
-      </c>
-      <c r="D5" s="13">
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11">
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <v>0</v>
       </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
-        <v>1</v>
-      </c>
-      <c r="N5" s="13">
-        <v>0</v>
-      </c>
-      <c r="O5" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="P5" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13">
-        <v>0</v>
-      </c>
-      <c r="S5" s="14">
-        <v>1</v>
-      </c>
-      <c r="T5" s="14">
-        <v>1</v>
-      </c>
-      <c r="U5" s="13">
+      <c r="F5" s="11">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="11">
+        <v>1</v>
+      </c>
+      <c r="P5" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>0</v>
+      </c>
+      <c r="R5" s="11">
+        <v>0</v>
+      </c>
+      <c r="S5" s="11">
+        <v>1</v>
+      </c>
+      <c r="T5" s="11">
+        <v>1</v>
+      </c>
+      <c r="U5" s="11">
         <v>0</v>
       </c>
     </row>
@@ -846,64 +855,64 @@
       <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="13">
-        <v>0</v>
-      </c>
-      <c r="C6" s="14">
-        <v>1</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
         <v>0</v>
       </c>
       <c r="F6" s="11">
         <v>0</v>
       </c>
-      <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="J6" s="13">
-        <v>0</v>
-      </c>
-      <c r="K6" s="13">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13">
-        <v>0</v>
-      </c>
-      <c r="M6" s="14">
-        <v>1</v>
-      </c>
-      <c r="N6" s="13">
-        <v>0</v>
-      </c>
-      <c r="O6" s="14">
-        <v>1</v>
-      </c>
-      <c r="P6" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>0</v>
-      </c>
-      <c r="R6" s="13">
-        <v>0</v>
-      </c>
-      <c r="S6" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="T6" s="14">
-        <v>1</v>
-      </c>
-      <c r="U6" s="13">
+      <c r="G6" s="11">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="11">
+        <v>1</v>
+      </c>
+      <c r="P6" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>0</v>
+      </c>
+      <c r="R6" s="11">
+        <v>0</v>
+      </c>
+      <c r="S6" s="11">
+        <v>2</v>
+      </c>
+      <c r="T6" s="11">
+        <v>1</v>
+      </c>
+      <c r="U6" s="11">
         <v>0</v>
       </c>
     </row>
@@ -911,64 +920,64 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0</v>
-      </c>
-      <c r="E7" s="13">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13">
-        <v>0</v>
-      </c>
-      <c r="K7" s="13">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <v>0</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0</v>
-      </c>
-      <c r="N7" s="13">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13">
-        <v>0</v>
-      </c>
-      <c r="P7" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>0</v>
-      </c>
-      <c r="R7" s="13">
-        <v>0</v>
-      </c>
-      <c r="S7" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="T7" s="13">
-        <v>0</v>
-      </c>
-      <c r="U7" s="13">
+      <c r="H7" s="11">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11">
+        <v>0</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>0</v>
+      </c>
+      <c r="R7" s="11">
+        <v>0</v>
+      </c>
+      <c r="S7" s="11">
+        <v>1</v>
+      </c>
+      <c r="T7" s="11">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11">
         <v>0</v>
       </c>
     </row>
@@ -976,64 +985,64 @@
       <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="14">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
         <v>0</v>
       </c>
       <c r="H8" s="11">
         <v>0</v>
       </c>
-      <c r="I8" s="14">
-        <v>1</v>
-      </c>
-      <c r="J8" s="13">
-        <v>0</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="13">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>0</v>
-      </c>
-      <c r="S8" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="T8" s="13">
-        <v>0</v>
-      </c>
-      <c r="U8" s="13">
+      <c r="I8" s="11">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>1</v>
+      </c>
+      <c r="T8" s="11">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1041,64 +1050,64 @@
       <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="13">
-        <v>0</v>
-      </c>
-      <c r="C9" s="12">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14">
+      <c r="B9" s="11">
+        <v>0</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11">
         <v>1</v>
       </c>
       <c r="I9" s="11">
         <v>0</v>
       </c>
-      <c r="J9" s="14">
-        <v>1</v>
-      </c>
-      <c r="K9" s="14">
-        <v>1</v>
-      </c>
-      <c r="L9" s="14">
-        <v>1</v>
-      </c>
-      <c r="M9" s="12">
-        <v>2</v>
-      </c>
-      <c r="N9" s="14">
-        <v>1</v>
-      </c>
-      <c r="O9" s="12">
-        <v>2</v>
-      </c>
-      <c r="P9" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="R9" s="14">
-        <v>1</v>
-      </c>
-      <c r="S9" s="12">
-        <v>2</v>
-      </c>
-      <c r="T9" s="12">
-        <v>2</v>
-      </c>
-      <c r="U9" s="14">
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11">
+        <v>1</v>
+      </c>
+      <c r="L9" s="11">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
+        <v>2</v>
+      </c>
+      <c r="N9" s="11">
+        <v>1</v>
+      </c>
+      <c r="O9" s="11">
+        <v>2</v>
+      </c>
+      <c r="P9" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>1</v>
+      </c>
+      <c r="R9" s="11">
+        <v>1</v>
+      </c>
+      <c r="S9" s="11">
+        <v>2</v>
+      </c>
+      <c r="T9" s="11">
+        <v>2</v>
+      </c>
+      <c r="U9" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1106,64 +1115,64 @@
       <c r="A10" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="14">
-        <v>1</v>
-      </c>
-      <c r="C10" s="13">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="14">
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
         <v>1</v>
       </c>
       <c r="J10" s="11">
         <v>0</v>
       </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13">
-        <v>0</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>1</v>
-      </c>
-      <c r="R10" s="13">
-        <v>0</v>
-      </c>
-      <c r="S10" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="T10" s="13">
-        <v>0</v>
-      </c>
-      <c r="U10" s="13">
+      <c r="K10" s="11">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
+      </c>
+      <c r="P10" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="11">
+        <v>1</v>
+      </c>
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <v>1</v>
+      </c>
+      <c r="T10" s="11">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1171,64 +1180,64 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="14">
-        <v>1</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="14">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="B11" s="11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11">
         <v>0</v>
       </c>
       <c r="K11" s="11">
         <v>0</v>
       </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="R11" s="13">
-        <v>0</v>
-      </c>
-      <c r="S11" s="14">
-        <v>1</v>
-      </c>
-      <c r="T11" s="13">
-        <v>0</v>
-      </c>
-      <c r="U11" s="13">
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
+      </c>
+      <c r="P11" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>1</v>
+      </c>
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+      <c r="S11" s="11">
+        <v>1</v>
+      </c>
+      <c r="T11" s="11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1236,64 +1245,64 @@
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="14">
-        <v>1</v>
-      </c>
-      <c r="J12" s="13">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="B12" s="11">
+        <v>1</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <v>0</v>
+      </c>
+      <c r="I12" s="11">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11">
         <v>0</v>
       </c>
       <c r="L12" s="11">
         <v>0</v>
       </c>
-      <c r="M12" s="13">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0</v>
-      </c>
-      <c r="P12" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="R12" s="13">
-        <v>0</v>
-      </c>
-      <c r="S12" s="14">
-        <v>1</v>
-      </c>
-      <c r="T12" s="13">
-        <v>0</v>
-      </c>
-      <c r="U12" s="13">
+      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+      <c r="N12" s="11">
+        <v>0</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
+      </c>
+      <c r="P12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>1</v>
+      </c>
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <v>1</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1301,64 +1310,64 @@
       <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="14">
-        <v>1</v>
-      </c>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="14">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0</v>
-      </c>
-      <c r="I13" s="14">
-        <v>2</v>
-      </c>
-      <c r="J13" s="13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="B13" s="11">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>2</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11">
         <v>0</v>
       </c>
       <c r="M13" s="11">
         <v>0</v>
       </c>
-      <c r="N13" s="13">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13">
-        <v>0</v>
-      </c>
-      <c r="P13" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="Q13" s="14">
-        <v>1</v>
-      </c>
-      <c r="R13" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="S13" s="13">
-        <v>0</v>
-      </c>
-      <c r="T13" s="13">
-        <v>0</v>
-      </c>
-      <c r="U13" s="13">
+      <c r="N13" s="11">
+        <v>0</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0</v>
+      </c>
+      <c r="P13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>1</v>
+      </c>
+      <c r="R13" s="11">
+        <v>1</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1366,64 +1375,64 @@
       <c r="A14" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="14">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="14">
-        <v>1</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
+      <c r="B14" s="11">
+        <v>1</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
+        <v>0</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11">
+        <v>0</v>
+      </c>
+      <c r="L14" s="11">
+        <v>0</v>
+      </c>
+      <c r="M14" s="11">
         <v>0</v>
       </c>
       <c r="N14" s="11">
         <v>0</v>
       </c>
-      <c r="O14" s="13">
-        <v>0</v>
-      </c>
-      <c r="P14" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>1</v>
-      </c>
-      <c r="R14" s="13">
-        <v>0</v>
-      </c>
-      <c r="S14" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="T14" s="13">
-        <v>0</v>
-      </c>
-      <c r="U14" s="13">
+      <c r="O14" s="11">
+        <v>0</v>
+      </c>
+      <c r="P14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="11">
+        <v>1</v>
+      </c>
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14" s="11">
+        <v>1</v>
+      </c>
+      <c r="T14" s="11">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1431,64 +1440,64 @@
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="14">
-        <v>1</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-      <c r="I15" s="12">
-        <v>2</v>
-      </c>
-      <c r="J15" s="13">
-        <v>0</v>
-      </c>
-      <c r="K15" s="13">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13">
-        <v>0</v>
-      </c>
-      <c r="N15" s="13">
+      <c r="B15" s="11">
+        <v>1</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2</v>
+      </c>
+      <c r="J15" s="11">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
+        <v>0</v>
+      </c>
+      <c r="N15" s="11">
         <v>0</v>
       </c>
       <c r="O15" s="11">
         <v>0</v>
       </c>
-      <c r="P15" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="Q15" s="14">
-        <v>1</v>
-      </c>
-      <c r="R15" s="14">
-        <v>1</v>
-      </c>
-      <c r="S15" s="13">
-        <v>0</v>
-      </c>
-      <c r="T15" s="13">
-        <v>0</v>
-      </c>
-      <c r="U15" s="13">
+      <c r="P15" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>1</v>
+      </c>
+      <c r="R15" s="11">
+        <v>1</v>
+      </c>
+      <c r="S15" s="11">
+        <v>0</v>
+      </c>
+      <c r="T15" s="11">
+        <v>0</v>
+      </c>
+      <c r="U15" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1496,64 +1505,64 @@
       <c r="A16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="13">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
-        <v>0</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="14">
-        <v>1</v>
-      </c>
-      <c r="J16" s="13">
-        <v>0</v>
-      </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="N16" s="13">
-        <v>0</v>
-      </c>
-      <c r="O16" s="14">
-        <v>0.5</v>
+      <c r="B16" s="11">
+        <v>0</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>1</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11">
+        <v>0</v>
+      </c>
+      <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
+        <v>1</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="11">
+        <v>1</v>
       </c>
       <c r="P16" s="11">
         <v>0</v>
       </c>
-      <c r="Q16" s="13">
-        <v>0</v>
-      </c>
-      <c r="R16" s="13">
-        <v>0</v>
-      </c>
-      <c r="S16" s="14">
-        <v>1</v>
-      </c>
-      <c r="T16" s="14">
-        <v>1</v>
-      </c>
-      <c r="U16" s="13">
+      <c r="Q16" s="11">
+        <v>0</v>
+      </c>
+      <c r="R16" s="11">
+        <v>0</v>
+      </c>
+      <c r="S16" s="11">
+        <v>1</v>
+      </c>
+      <c r="T16" s="11">
+        <v>1</v>
+      </c>
+      <c r="U16" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1561,64 +1570,64 @@
       <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="13">
-        <v>0</v>
-      </c>
-      <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="J17" s="14">
-        <v>1</v>
-      </c>
-      <c r="K17" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="L17" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="M17" s="14">
-        <v>1</v>
-      </c>
-      <c r="N17" s="14">
-        <v>1</v>
-      </c>
-      <c r="O17" s="14">
-        <v>1</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="B17" s="11">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="11">
+        <v>1</v>
+      </c>
+      <c r="K17" s="11">
+        <v>1</v>
+      </c>
+      <c r="L17" s="11">
+        <v>1</v>
+      </c>
+      <c r="M17" s="11">
+        <v>1</v>
+      </c>
+      <c r="N17" s="11">
+        <v>1</v>
+      </c>
+      <c r="O17" s="11">
+        <v>1</v>
+      </c>
+      <c r="P17" s="11">
         <v>0</v>
       </c>
       <c r="Q17" s="11">
         <v>0</v>
       </c>
-      <c r="R17" s="13">
-        <v>0</v>
-      </c>
-      <c r="S17" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="T17" s="14">
-        <v>1</v>
-      </c>
-      <c r="U17" s="13">
+      <c r="R17" s="11">
+        <v>0</v>
+      </c>
+      <c r="S17" s="11">
+        <v>2</v>
+      </c>
+      <c r="T17" s="11">
+        <v>1</v>
+      </c>
+      <c r="U17" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1626,64 +1635,64 @@
       <c r="A18" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="13">
-        <v>0</v>
-      </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
-      <c r="I18" s="14">
-        <v>1</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="14">
-        <v>1</v>
-      </c>
-      <c r="P18" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13">
+      <c r="B18" s="11">
+        <v>0</v>
+      </c>
+      <c r="C18" s="11">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11">
+        <v>0</v>
+      </c>
+      <c r="L18" s="11">
+        <v>0</v>
+      </c>
+      <c r="M18" s="11">
+        <v>1</v>
+      </c>
+      <c r="N18" s="11">
+        <v>0</v>
+      </c>
+      <c r="O18" s="11">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
         <v>0</v>
       </c>
       <c r="R18" s="11">
         <v>0</v>
       </c>
-      <c r="S18" s="14">
-        <v>1</v>
-      </c>
-      <c r="T18" s="14">
-        <v>1</v>
-      </c>
-      <c r="U18" s="13">
+      <c r="S18" s="11">
+        <v>1</v>
+      </c>
+      <c r="T18" s="11">
+        <v>1</v>
+      </c>
+      <c r="U18" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1691,64 +1700,64 @@
       <c r="A19" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="12">
-        <v>2</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="E19" s="14">
-        <v>1</v>
-      </c>
-      <c r="F19" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="H19" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="12">
-        <v>2</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="K19" s="14">
-        <v>1</v>
-      </c>
-      <c r="L19" s="14">
-        <v>1</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
-      </c>
-      <c r="N19" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="O19" s="13">
-        <v>0</v>
-      </c>
-      <c r="P19" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="R19" s="14">
+      <c r="B19" s="11">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
+        <v>2</v>
+      </c>
+      <c r="E19" s="11">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11">
+        <v>2</v>
+      </c>
+      <c r="G19" s="11">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11">
+        <v>1</v>
+      </c>
+      <c r="I19" s="11">
+        <v>2</v>
+      </c>
+      <c r="J19" s="11">
+        <v>1</v>
+      </c>
+      <c r="K19" s="11">
+        <v>1</v>
+      </c>
+      <c r="L19" s="11">
+        <v>1</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11">
+        <v>1</v>
+      </c>
+      <c r="O19" s="11">
+        <v>0</v>
+      </c>
+      <c r="P19" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>2</v>
+      </c>
+      <c r="R19" s="11">
         <v>1</v>
       </c>
       <c r="S19" s="11">
         <v>0</v>
       </c>
-      <c r="T19" s="13">
-        <v>0</v>
-      </c>
-      <c r="U19" s="14">
+      <c r="T19" s="11">
+        <v>0</v>
+      </c>
+      <c r="U19" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1756,64 +1765,64 @@
       <c r="A20" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="14">
-        <v>1</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14">
-        <v>1</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12">
-        <v>2</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="14">
-        <v>1</v>
-      </c>
-      <c r="R20" s="14">
-        <v>1</v>
-      </c>
-      <c r="S20" s="13">
+      <c r="B20" s="11">
+        <v>1</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11">
+        <v>1</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <v>2</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0</v>
+      </c>
+      <c r="K20" s="11">
+        <v>0</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
+      <c r="O20" s="11">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>1</v>
+      </c>
+      <c r="R20" s="11">
+        <v>1</v>
+      </c>
+      <c r="S20" s="11">
         <v>0</v>
       </c>
       <c r="T20" s="11">
         <v>0</v>
       </c>
-      <c r="U20" s="13">
+      <c r="U20" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1821,66 +1830,509 @@
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="13">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14">
-        <v>1</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14">
-        <v>1</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13">
-        <v>0</v>
-      </c>
-      <c r="O21" s="13">
-        <v>0</v>
-      </c>
-      <c r="P21" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="13">
-        <v>0</v>
-      </c>
-      <c r="R21" s="13">
-        <v>0</v>
-      </c>
-      <c r="S21" s="14">
-        <v>1</v>
-      </c>
-      <c r="T21" s="13">
+      <c r="B21" s="11">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>1</v>
+      </c>
+      <c r="J21" s="11">
+        <v>0</v>
+      </c>
+      <c r="K21" s="11">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11">
+        <v>0</v>
+      </c>
+      <c r="N21" s="11">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="11">
+        <v>0</v>
+      </c>
+      <c r="R21" s="11">
+        <v>0</v>
+      </c>
+      <c r="S21" s="11">
+        <v>1</v>
+      </c>
+      <c r="T21" s="11">
         <v>0</v>
       </c>
       <c r="U21" s="11">
         <v>0</v>
       </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="11"/>
+      <c r="P36" s="11"/>
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+      <c r="T36" s="11"/>
+      <c r="U36" s="11"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11"/>
+      <c r="S40" s="11"/>
+      <c r="T40" s="11"/>
+      <c r="U40" s="11"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B43" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1888,7 +2340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3260,7 +3712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
